--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486283_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486283_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7221</v>
+        <v>3.9843</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3257</v>
+        <v>4.6804</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6036</v>
+        <v>-0.6961000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>1.0006</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2865</v>
+        <v>1.5487</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7797</v>
+        <v>1.1344</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5067</v>
+        <v>0.4143</v>
       </c>
       <c r="V2" t="n">
         <v>0.5649999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4246</v>
+        <v>0.5123</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3033</v>
+        <v>2.3602</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8787</v>
+        <v>-1.8479</v>
       </c>
       <c r="G3" t="n">
         <v>-1.6819</v>
@@ -688,13 +688,13 @@
         <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1548</v>
+        <v>0.2424</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1328</v>
+        <v>1.1897</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9781</v>
+        <v>-0.9472</v>
       </c>
       <c r="V3" t="n">
         <v>1.9517</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5779</v>
+        <v>-0.1825</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7398</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1618</v>
+        <v>-0.1825</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.345</v>
+        <v>-0.1825</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4989</v>
+        <v>-0.1825</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.8439</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0051</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5972</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5921</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3502</v>
+        <v>-0.1825</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0983</v>
+        <v>-0.1825</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2519</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3155</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7797</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5358000000000001</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1641</v>
+        <v>-0.1829</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2424</v>
+        <v>1.318</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4065</v>
+        <v>-1.5009</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.1201</v>
+        <v>-1.345</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8276</v>
+        <v>0.4989</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2925</v>
+        <v>-1.8439</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5373</v>
+        <v>1.0051</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0547</v>
+        <v>1.5972</v>
       </c>
       <c r="L5" t="n">
         <v>-0.5921</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5827</v>
+        <v>-2.3502</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8823</v>
+        <v>-1.0983</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7004</v>
+        <v>-1.2519</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>1.956</v>
+        <v>1.5547</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7797</v>
+        <v>1.3579</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1763</v>
+        <v>0.1968</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1825</v>
+        <v>-0.3436</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-0.9933</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1825</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1825</v>
+        <v>0.3966</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1825</v>
+        <v>-0.9947</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.3913</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0.0271</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.5172</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1825</v>
+        <v>0.4238</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1825</v>
+        <v>-0.4504</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.8741</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.2145</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.1214</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.3359</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3082</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3082</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.256</v>
+        <v>-0.9018</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8441</v>
+        <v>0.5971</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5881</v>
+        <v>-1.4989</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3966</v>
+        <v>-2.1201</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9947</v>
+        <v>-0.8276</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3913</v>
+        <v>-1.2925</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0271</v>
+        <v>-0.5373</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5443</v>
+        <v>0.0547</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5172</v>
+        <v>-0.5921</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4238</v>
+        <v>-1.5827</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4504</v>
+        <v>-0.8823</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8741</v>
+        <v>-0.7004</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.127</v>
+        <v>1.2182</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7294</v>
+        <v>1.1344</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3975</v>
+        <v>0.0838</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3082</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3082</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5603</v>
+        <v>-2.461</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0288</v>
+        <v>0.0973</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5891</v>
+        <v>-2.5583</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3607</v>
@@ -1078,13 +1078,13 @@
         <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.197</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2211</v>
+        <v>0.2896</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4181</v>
+        <v>-0.3873</v>
       </c>
       <c r="V8" t="n">
         <v>-2.7427</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PERIS CRESPO</t>
+          <t>C. ROGERS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6451</v>
+        <v>-2.6195</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.23</v>
+        <v>-2.427</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4151</v>
+        <v>-0.1925</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.8262</v>
+        <v>-0.9031</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2648</v>
+        <v>-1.0434</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.0911</v>
+        <v>0.1403</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8905</v>
+        <v>-0.2295</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0132</v>
+        <v>-0.1762</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.9037</v>
+        <v>-0.0533</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9357</v>
+        <v>-0.6736</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7484</v>
+        <v>-0.8672</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1873</v>
+        <v>0.1936</v>
       </c>
       <c r="P9" t="n">
-        <v>0.435</v>
+        <v>-3.4801</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6407</v>
+        <v>1.0241</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5119</v>
+        <v>1.0227</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1288</v>
+        <v>0.0015</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3867</v>
+        <v>0.7395</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2599</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8732</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. ROGERS</t>
+          <t>J. PERIS CRESPO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0668</v>
+        <v>-2.6903</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9051</v>
+        <v>-0.491</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1617</v>
+        <v>-2.1994</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9031</v>
+        <v>-3.8262</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0434</v>
+        <v>0.2648</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1403</v>
+        <v>-4.0911</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2295</v>
+        <v>-1.8905</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1762</v>
+        <v>1.0132</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0533</v>
+        <v>-2.9037</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6736</v>
+        <v>-1.9357</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8672</v>
+        <v>-0.7484</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1936</v>
+        <v>-1.1873</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.4801</v>
+        <v>0.435</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4231</v>
+        <v>-0.6859</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4554</v>
+        <v>0.2271</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0323</v>
+        <v>-0.913</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7395</v>
+        <v>1.3867</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>2.2599</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3904</v>
+        <v>-0.8732</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. NASPLER PERAIRE</t>
+          <t>T. ROBERTS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3163</v>
+        <v>-3.7711</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6523</v>
+        <v>-2.0409</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6639</v>
+        <v>-1.7301</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7287</v>
+        <v>-2.8396</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4052</v>
+        <v>-3.1687</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6765</v>
+        <v>0.3292</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-1.4345</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6903</v>
+        <v>-2.186</v>
       </c>
       <c r="L11" t="n">
-        <v>0.612</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6504</v>
+        <v>-1.4051</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7149</v>
+        <v>-0.9827</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0645</v>
+        <v>-0.4224</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5225</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8221000000000001</v>
+        <v>0.286</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.399</v>
+        <v>0.4386</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4231</v>
+        <v>-0.1526</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.243</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.243</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. ROBERTS</t>
+          <t>T. NASPLER PERAIRE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1172</v>
+        <v>-3.9001</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1405</v>
+        <v>-2.2053</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9767</v>
+        <v>-1.6947</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8396</v>
+        <v>-0.7287</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.1687</v>
+        <v>-1.4052</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3292</v>
+        <v>0.6765</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4345</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.186</v>
+        <v>-0.6903</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.612</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4051</v>
+        <v>-0.6504</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9827</v>
+        <v>-0.7149</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4224</v>
+        <v>0.0645</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6525</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0601</v>
+        <v>-0.4059</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6609</v>
+        <v>0.0481</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3992</v>
+        <v>-0.4539</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.243</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.695</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.5837</v>
+        <v>-12.5562</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1320000000000006</v>
+        <v>0.8955000000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.4515</v>
+        <v>-13.4516</v>
       </c>
       <c r="G13" t="n">
         <v>-13.5906</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.9529</v>
+        <v>-7.952900000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-5.6377</v>
@@ -1444,10 +1444,10 @@
         <v>-1.556</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7027999999999999</v>
+        <v>0.7028000000000004</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.258900000000001</v>
+        <v>-2.2589</v>
       </c>
       <c r="M13" t="n">
         <v>-12.0345</v>
@@ -1456,28 +1456,28 @@
         <v>-8.6556</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.3789</v>
+        <v>-3.378900000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.350000000000001</v>
+        <v>-4.35</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.1379</v>
       </c>
       <c r="R13" t="n">
-        <v>9.787600000000001</v>
+        <v>9.787599999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>3.442799999999999</v>
+        <v>4.470199999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>5.9364</v>
+        <v>6.963900000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.4937</v>
+        <v>-2.4935</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9139999999999999</v>
+        <v>0.9140000000000004</v>
       </c>
       <c r="W13" t="n">
         <v>9.625499999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>G. KALSCHEUR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3716</v>
+        <v>3.9763</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7811</v>
+        <v>4.2937</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5905</v>
+        <v>-0.3174</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7316</v>
+        <v>3.2018</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4447</v>
+        <v>2.6639</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2869</v>
+        <v>0.5379</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4903</v>
+        <v>2.7008</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3756</v>
+        <v>2.7191</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1147</v>
+        <v>-0.0183</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2413</v>
+        <v>0.501</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.0552</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1722</v>
+        <v>0.5562</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.305</v>
+        <v>1.305</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4898</v>
+        <v>-0.5306</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0106</v>
+        <v>-0.1021</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5208</v>
+        <v>-0.4284</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4552</v>
+        <v>1.695</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. KALSCHEUR</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4792</v>
+        <v>3.8385</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1819</v>
+        <v>3.2223</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7027</v>
+        <v>0.6162</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2018</v>
+        <v>2.7316</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6639</v>
+        <v>1.4447</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5379</v>
+        <v>1.2869</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7008</v>
+        <v>2.4903</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7191</v>
+        <v>2.3756</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0183</v>
+        <v>0.1147</v>
       </c>
       <c r="M15" t="n">
-        <v>0.501</v>
+        <v>0.2413</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0552</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5562</v>
+        <v>1.1722</v>
       </c>
       <c r="P15" t="n">
-        <v>1.305</v>
+        <v>-1.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0277</v>
+        <v>-0.0433</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2139</v>
+        <v>0.4518</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8138</v>
+        <v>-0.4951</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="W15" t="n">
-        <v>1.695</v>
+        <v>2.4552</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>M. FERNANDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0993</v>
+        <v>2.8018</v>
       </c>
       <c r="E16" t="n">
-        <v>2.06</v>
+        <v>1.4466</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0394</v>
+        <v>1.3551</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2276</v>
+        <v>2.3535</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2475</v>
+        <v>1.3869</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0199</v>
+        <v>0.9666</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1369</v>
+        <v>0.9503</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3719</v>
+        <v>0.2618</v>
       </c>
       <c r="L16" t="n">
-        <v>0.765</v>
+        <v>0.6885</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0907</v>
+        <v>1.4032</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8757</v>
+        <v>1.1251</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7849</v>
+        <v>0.2781</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.435</v>
+        <v>0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3067</v>
+        <v>0.0132</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0106</v>
+        <v>0.4963</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2961</v>
+        <v>-0.4831</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARBALLO</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5179</v>
+        <v>2.7348</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5584</v>
+        <v>3.8942</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9595</v>
+        <v>-1.1594</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3535</v>
+        <v>2.0532</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3869</v>
+        <v>-0.6538</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9666</v>
+        <v>2.707</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9503</v>
+        <v>3.6257</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2618</v>
+        <v>0.9434</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6885</v>
+        <v>2.6823</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4032</v>
+        <v>-1.5725</v>
       </c>
       <c r="N17" t="n">
-        <v>1.1251</v>
+        <v>-1.5972</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2781</v>
+        <v>0.0247</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>0.435</v>
+        <v>2.3926</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2706</v>
+        <v>-0.6234</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6081</v>
+        <v>-0.3389</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8787</v>
+        <v>-0.2845</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7188</v>
+        <v>2.5418</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6938</v>
+        <v>1.3894</v>
       </c>
       <c r="F18" t="n">
-        <v>1.025</v>
+        <v>1.1524</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2005</v>
+        <v>2.2276</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3893</v>
+        <v>2.2475</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8112</v>
+        <v>-0.0199</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.1057</v>
+        <v>2.1369</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3989</v>
+        <v>1.3719</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7068</v>
+        <v>0.765</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9052</v>
+        <v>0.0907</v>
       </c>
       <c r="N18" t="n">
-        <v>1.0096</v>
+        <v>0.8757</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1044</v>
+        <v>-0.7849</v>
       </c>
       <c r="P18" t="n">
-        <v>0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2107</v>
+        <v>0.7493</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5396</v>
+        <v>0.3401</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7502</v>
+        <v>0.4092</v>
       </c>
       <c r="V18" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.178</v>
+        <v>2.1954</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0002</v>
+        <v>0.8056</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8222</v>
+        <v>1.3898</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0532</v>
+        <v>-1.2005</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6538</v>
+        <v>-0.3893</v>
       </c>
       <c r="I19" t="n">
-        <v>2.707</v>
+        <v>-0.8112</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6257</v>
+        <v>-2.1057</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9434</v>
+        <v>-1.3989</v>
       </c>
       <c r="L19" t="n">
-        <v>2.6823</v>
+        <v>-0.7068</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5725</v>
+        <v>0.9052</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5972</v>
+        <v>1.0096</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0247</v>
+        <v>-0.1044</v>
       </c>
       <c r="P19" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.1802</v>
+        <v>0.2659</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2329</v>
+        <v>0.6513</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9473</v>
+        <v>-0.3854</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="W19" t="n">
-        <v>1.695</v>
+        <v>2.2599</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7257</v>
+        <v>1.6583</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6277</v>
+        <v>0.0429</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3534</v>
+        <v>1.6155</v>
       </c>
       <c r="G20" t="n">
         <v>1.8989</v>
@@ -2014,13 +2014,13 @@
         <v>2.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8035</v>
+        <v>0.1292</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2139</v>
+        <v>0.4567</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5896</v>
+        <v>-0.3275</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3698</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.597</v>
+        <v>1.0248</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.7486</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2633</v>
+        <v>0.2762</v>
       </c>
       <c r="G21" t="n">
         <v>1.1897</v>
@@ -2092,13 +2092,13 @@
         <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6149</v>
+        <v>-0.1872</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3341</v>
+        <v>0.2223</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.949</v>
+        <v>-0.4095</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4356</v>
+        <v>0.4664</v>
       </c>
       <c r="E22" t="n">
         <v>-0.169</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6046</v>
+        <v>0.6354</v>
       </c>
       <c r="G22" t="n">
         <v>0.1855</v>
@@ -2170,13 +2170,13 @@
         <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1849</v>
+        <v>-0.1541</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2055</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2409</v>
+        <v>-0.481</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4167</v>
+        <v>0.3049</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6575</v>
+        <v>-0.7859</v>
       </c>
       <c r="G23" t="n">
         <v>1.0226</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>0.214</v>
+        <v>-0.0261</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2656</v>
+        <v>0.1538</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0516</v>
+        <v>-0.18</v>
       </c>
       <c r="V23" t="n">
         <v>-1.695</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.858</v>
+        <v>-1.944</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7299</v>
+        <v>-1.8417</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1281</v>
+        <v>-0.1024</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1798</v>
@@ -2326,13 +2326,13 @@
         <v>0.2175</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1918</v>
+        <v>0.1057</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3341</v>
+        <v>0.2223</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1423</v>
+        <v>-0.1166</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4405</v>
+        <v>-2.2491</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.6859</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8664</v>
+        <v>-1.5632</v>
       </c>
       <c r="G25" t="n">
         <v>-0.8935999999999999</v>
@@ -2404,13 +2404,13 @@
         <v>2.1751</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3527</v>
+        <v>-0.1613</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2572</v>
+        <v>0.1454</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6099</v>
+        <v>-0.3067</v>
       </c>
       <c r="V25" t="n">
         <v>-3.3692</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>13.5837</v>
+        <v>16.564</v>
       </c>
       <c r="E26" t="n">
-        <v>13.4518</v>
+        <v>13.4516</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1322000000000005</v>
+        <v>3.112299999999999</v>
       </c>
       <c r="G26" t="n">
         <v>13.5905</v>
@@ -2467,7 +2467,7 @@
         <v>1.5561</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.7030000000000001</v>
+        <v>-0.7029999999999998</v>
       </c>
       <c r="O26" t="n">
         <v>2.259</v>
@@ -2482,13 +2482,13 @@
         <v>14.1378</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.4429</v>
+        <v>-0.4626999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4937</v>
+        <v>2.4935</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.936599999999999</v>
+        <v>-2.9562</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9141000000000004</v>
